--- a/FichierControleFluxCoteUnix/rapport/03082026_FOURNISSEUR_IGP.xlsx
+++ b/FichierControleFluxCoteUnix/rapport/03082026_FOURNISSEUR_IGP.xlsx
@@ -774,7 +774,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fichier : FAC02_SRC_FACTURESFOURNISSEURS_180726-011630_ST_FAC02_639199341908753475_001  |  Execution : 25/08/2026 14:17:32</t>
+          <t>Fichier : FAC02_SRC_FACTURESFOURNISSEURS_180726-011630_ST_FAC02_639199341908753475_001  |  Execution : 25/08/2026 20:34:33</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fichier : FAC02_SRC_FACTURESFOURNISSEURS_180726-011630_ST_FAC02_639199341908753475_001  |  Execution : 25/08/2026 14:17:32</t>
+          <t>Fichier : FAC02_SRC_FACTURESFOURNISSEURS_180726-011630_ST_FAC02_639199341908753475_001  |  Execution : 25/08/2026 20:34:33</t>
         </is>
       </c>
     </row>
